--- a/artfynd/A 62169-2022 artfynd.xlsx
+++ b/artfynd/A 62169-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1559,6 +1559,228 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114700540</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97528</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nysätra (5), Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>667031</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6646147</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>C-Upp-0880</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-01-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-01-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Baltasar Pinheiro, Andreas Persson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114700541</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97528</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nysätra (4), Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>666959</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6646209</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>C-Upp-0879</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-01-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-01-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Baltasar Pinheiro, Andreas Persson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62169-2022 artfynd.xlsx
+++ b/artfynd/A 62169-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62169-2022 artfynd.xlsx
+++ b/artfynd/A 62169-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1559,228 +1559,6 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>114700540</v>
-      </c>
-      <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Nysätra (5), Upl</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>667031</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6646147</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Rasbo</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>C-Upp-0880</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-01-15</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-01-15</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Baltasar Pinheiro, Andreas Persson, Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>114700541</v>
-      </c>
-      <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Nysätra (4), Upl</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>666959</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6646209</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Rasbo</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>C-Upp-0879</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2023-01-15</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2023-01-15</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Baltasar Pinheiro, Andreas Persson, Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
